--- a/outputs/issues/issue_label_frequency.xlsx
+++ b/outputs/issues/issue_label_frequency.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Crowd and Wait Time</t>
+          <t>Service Issues</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -441,7 +441,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Service Issues</t>
+          <t>Crowd and Wait Time</t>
         </is>
       </c>
       <c r="B3" t="n">
